--- a/resource/test_task.xlsx
+++ b/resource/test_task.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>任务类型</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>inbound</t>
+  </si>
+  <si>
+    <t>outbound</t>
   </si>
 </sst>
 </file>
@@ -1190,8 +1193,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1229,70 +1232,36 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/resource/test_task.xlsx
+++ b/resource/test_task.xlsx
@@ -1258,10 +1258,10 @@
         <v>6</v>
       </c>
       <c r="D4" s="1">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1">
         <v>15</v>
-      </c>
-      <c r="E4" s="1">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/resource/test_task.xlsx
+++ b/resource/test_task.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>任务类型</t>
   </si>
@@ -1193,8 +1193,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1244,23 +1244,6 @@
         <v>18</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1">
         <v>15</v>
       </c>
     </row>

--- a/resource/test_task.xlsx
+++ b/resource/test_task.xlsx
@@ -1235,7 +1235,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>6</v>
